--- a/data/catalogs/service_mappings.xlsx
+++ b/data/catalogs/service_mappings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,12 +479,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Khoa Nội</t>
+          <t>Khoa Ngoại tổng hợp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Siêu âm</t>
+          <t>Nội soi</t>
         </is>
       </c>
     </row>
@@ -496,26 +496,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Xét nghiệm</t>
+          <t>Siêu âm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Khoa Cấp cứu</t>
+          <t>Khoa Nội</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cấp cứu</t>
+          <t>X-quang</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Khoa Cấp cứu</t>
+          <t>Khoa Nội</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,19 +527,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Khoa Cấp cứu</t>
+          <t>Khoa Nội</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>X-quang</t>
+          <t>Thăm dò chức năng</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Khoa Phụ Sản</t>
+          <t>Khoa Cấp cứu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -551,12 +551,84 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Khoa Cấp cứu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>X-quang</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Khoa Cấp cứu</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Xét nghiệm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Khoa Cấp cứu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CT Scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Khoa Phụ Sản</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Siêu âm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Khoa Phụ Sản</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Xét nghiệm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Khoa Phẫu thuật - GMHS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Xét nghiệm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Khoa Phẫu thuật - GMHS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>X-quang</t>
         </is>
       </c>
     </row>
